--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.5868,0.0201,0.0638,0.3635</t>
-  </si>
-  <si>
-    <t>0.0625,0.0028,0.0052,0.9716</t>
-  </si>
-  <si>
-    <t>0.8808,0.0018,0.0018,0.1503</t>
-  </si>
-  <si>
-    <t>0.0950,0.0012,0.0043,0.9610</t>
-  </si>
-  <si>
-    <t>0.9972,0.0005,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9932,0.0045,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9876,0.0083,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.9933,0.0036,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9950,0.0033,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9856,0.0122,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9944,0.0020,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9984,0.0004,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.5562,0.3781,0.0502,0.0870</t>
-  </si>
-  <si>
-    <t>0.2669,0.0134,0.8400,0.0003</t>
-  </si>
-  <si>
-    <t>0.6119,0.0110,0.5579,0.0013</t>
-  </si>
-  <si>
-    <t>0.6102,0.0139,0.5380,0.0012</t>
-  </si>
-  <si>
-    <t>0.5503,0.2764,0.2011,0.0096</t>
-  </si>
-  <si>
-    <t>0.0056,0.9905,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.0101,0.9854,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.4423,0.6756,0.0079,0.0024</t>
-  </si>
-  <si>
-    <t>0.2956,0.8222,0.0018,0.0020</t>
-  </si>
-  <si>
-    <t>0.0046,0.9939,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.6004,0.0121,0.4510,0.0131</t>
-  </si>
-  <si>
-    <t>0.6926,0.0089,0.3001,0.0164</t>
-  </si>
-  <si>
-    <t>0.0177,0.0132,0.9773,0.0007</t>
-  </si>
-  <si>
-    <t>0.3471,0.0276,0.7564,0.0056</t>
-  </si>
-  <si>
-    <t>0.0497,0.0075,0.9605,0.0010</t>
-  </si>
-  <si>
-    <t>0.1620,0.0122,0.8745,0.0053</t>
-  </si>
-  <si>
-    <t>0.0248,0.0010,0.9801,0.0018</t>
-  </si>
-  <si>
-    <t>0.1313,0.8381,0.0199,0.0083</t>
-  </si>
-  <si>
-    <t>0.6713,0.2291,0.1572,0.0129</t>
-  </si>
-  <si>
-    <t>0.0002,0.0022,0.9987,0.0003</t>
-  </si>
-  <si>
-    <t>0.0030,0.9590,0.1816,0.0002</t>
-  </si>
-  <si>
-    <t>0.7533,0.3087,0.0097,0.0076</t>
-  </si>
-  <si>
-    <t>0.6038,0.0717,0.3042,0.0009</t>
-  </si>
-  <si>
-    <t>0.6152,0.5275,0.0069,0.0033</t>
-  </si>
-  <si>
-    <t>0.0705,0.8979,0.1508,0.0131</t>
-  </si>
-  <si>
-    <t>0.0339,0.3193,0.7899,0.0209</t>
-  </si>
-  <si>
-    <t>0.0157,0.1524,0.9718,0.0068</t>
-  </si>
-  <si>
-    <t>0.0981,0.1394,0.8436,0.0071</t>
-  </si>
-  <si>
-    <t>0.2270,0.0059,0.8079,0.0130</t>
-  </si>
-  <si>
-    <t>0.0037,0.0346,0.9734,0.0127</t>
-  </si>
-  <si>
-    <t>0.0051,0.9731,0.0057,0.0004</t>
-  </si>
-  <si>
-    <t>0.0221,0.1143,0.9314,0.0069</t>
-  </si>
-  <si>
-    <t>0.0093,0.8951,0.0019,0.4117</t>
-  </si>
-  <si>
-    <t>0.0070,0.9816,0.0071,0.0026</t>
-  </si>
-  <si>
-    <t>0.0034,0.9850,0.0429,0.0007</t>
-  </si>
-  <si>
-    <t>0.0076,0.9643,0.0131,0.0213</t>
-  </si>
-  <si>
-    <t>0.0078,0.1827,0.9437,0.0167</t>
-  </si>
-  <si>
-    <t>0.0029,0.1898,0.9812,0.0008</t>
-  </si>
-  <si>
-    <t>0.1524,0.0661,0.8007,0.0035</t>
-  </si>
-  <si>
-    <t>0.0229,0.0006,0.9882,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.0022,0.9948,0.0116</t>
-  </si>
-  <si>
-    <t>0.0092,0.0084,0.9769,0.0045</t>
-  </si>
-  <si>
-    <t>0.9600,0.0511,0.0056,0.0009</t>
-  </si>
-  <si>
-    <t>0.9740,0.0071,0.0143,0.0020</t>
-  </si>
-  <si>
-    <t>0.9579,0.0399,0.0091,0.0015</t>
-  </si>
-  <si>
-    <t>0.0011,0.0745,0.9906,0.0012</t>
-  </si>
-  <si>
-    <t>0.9860,0.0061,0.0040,0.0010</t>
-  </si>
-  <si>
-    <t>0.9879,0.0085,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9689,0.0458,0.0022,0.0004</t>
-  </si>
-  <si>
-    <t>0.0021,0.8820,0.9370,0.0007</t>
-  </si>
-  <si>
-    <t>0.0028,0.0119,0.9777,0.0246</t>
-  </si>
-  <si>
-    <t>0.0165,0.0707,0.9330,0.0277</t>
-  </si>
-  <si>
-    <t>0.0004,0.8980,0.9839,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.0105,0.9941,0.0013</t>
-  </si>
-  <si>
-    <t>0.0564,0.9048,0.0337,0.0001</t>
-  </si>
-  <si>
-    <t>0.0136,0.9861,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.5610,0.0332,0.5526,0.0137</t>
-  </si>
-  <si>
-    <t>0.1633,0.8230,0.0615,0.0093</t>
-  </si>
-  <si>
-    <t>0.0046,0.0145,0.9818,0.0039</t>
-  </si>
-  <si>
-    <t>0.0055,0.8671,0.6580,0.0004</t>
-  </si>
-  <si>
-    <t>0.0022,0.6867,0.9284,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.9833,0.2269,0.0009</t>
-  </si>
-  <si>
-    <t>0.0005,0.8951,0.9610,0.0001</t>
-  </si>
-  <si>
-    <t>0.2384,0.0067,0.0797,0.7312</t>
-  </si>
-  <si>
-    <t>0.0002,0.0870,0.0004,0.9979</t>
-  </si>
-  <si>
-    <t>0.0089,0.0058,0.0030,0.9937</t>
-  </si>
-  <si>
-    <t>0.1121,0.0046,0.0015,0.9535</t>
-  </si>
-  <si>
-    <t>0.0405,0.0077,0.0026,0.9812</t>
-  </si>
-  <si>
-    <t>0.0011,0.0016,0.0007,0.9990</t>
-  </si>
-  <si>
-    <t>0.0005,0.9794,0.6630,0.0000</t>
-  </si>
-  <si>
-    <t>0.0066,0.5647,0.9447,0.0008</t>
-  </si>
-  <si>
-    <t>0.0017,0.8257,0.9235,0.0003</t>
-  </si>
-  <si>
-    <t>0.0104,0.4308,0.9284,0.0031</t>
-  </si>
-  <si>
-    <t>0.0003,0.9812,0.7724,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.8549,0.8373,0.0010</t>
-  </si>
-  <si>
-    <t>0.9938,0.0041,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9647,0.0359,0.0029,0.0019</t>
-  </si>
-  <si>
-    <t>0.9023,0.1547,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.9923,0.0048,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9703,0.0249,0.0003,0.0024</t>
-  </si>
-  <si>
-    <t>0.9883,0.0085,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.9919,0.0068,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9901,0.0046,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0000,0.0008</t>
-  </si>
-  <si>
-    <t>0.9972,0.0010,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9965,0.0018,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9939,0.0033,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9966,0.0004,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.9941,0.0023,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9972,0.0006,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9965,0.0006,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.0161,0.0042,0.9732,0.0123</t>
-  </si>
-  <si>
-    <t>0.2787,0.0087,0.7895,0.0071</t>
-  </si>
-  <si>
-    <t>0.9008,0.0043,0.1073,0.0021</t>
-  </si>
-  <si>
-    <t>0.1504,0.0024,0.9261,0.0011</t>
-  </si>
-  <si>
-    <t>0.0356,0.9578,0.0046,0.0008</t>
-  </si>
-  <si>
-    <t>0.1020,0.8996,0.0327,0.0014</t>
-  </si>
-  <si>
-    <t>0.0252,0.9613,0.0003,0.0019</t>
-  </si>
-  <si>
-    <t>0.3654,0.7231,0.0112,0.0031</t>
-  </si>
-  <si>
-    <t>0.0246,0.9690,0.0088,0.0011</t>
-  </si>
-  <si>
-    <t>0.0005,0.9974,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.7551,0.3062,0.0219,0.0033</t>
-  </si>
-  <si>
-    <t>0.4454,0.3481,0.2044,0.0882</t>
-  </si>
-  <si>
-    <t>0.6226,0.0147,0.4456,0.0156</t>
-  </si>
-  <si>
-    <t>0.6559,0.1372,0.1867,0.0297</t>
-  </si>
-  <si>
-    <t>0.6061,0.0330,0.4563,0.0049</t>
-  </si>
-  <si>
-    <t>0.0372,0.2140,0.0328,0.9248</t>
-  </si>
-  <si>
-    <t>0.0083,0.9835,0.0115,0.0009</t>
-  </si>
-  <si>
-    <t>0.0021,0.9831,0.0040,0.0113</t>
-  </si>
-  <si>
-    <t>0.0167,0.9425,0.0118,0.0550</t>
-  </si>
-  <si>
-    <t>0.0025,0.8373,0.8995,0.0004</t>
-  </si>
-  <si>
-    <t>0.0350,0.9493,0.0624,0.0028</t>
-  </si>
-  <si>
-    <t>0.4662,0.6510,0.0189,0.0010</t>
-  </si>
-  <si>
-    <t>0.5890,0.5329,0.0168,0.0021</t>
-  </si>
-  <si>
-    <t>0.9413,0.0486,0.0076,0.0057</t>
-  </si>
-  <si>
-    <t>0.9904,0.0026,0.0009,0.0016</t>
-  </si>
-  <si>
-    <t>0.9914,0.0007,0.0009,0.0025</t>
-  </si>
-  <si>
-    <t>0.9895,0.0045,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.9857,0.0032,0.0003,0.0049</t>
-  </si>
-  <si>
-    <t>0.8649,0.0916,0.0520,0.0042</t>
-  </si>
-  <si>
-    <t>0.9795,0.0111,0.0021,0.0036</t>
-  </si>
-  <si>
-    <t>0.9818,0.0057,0.0043,0.0024</t>
-  </si>
-  <si>
-    <t>0.0046,0.3930,0.9728,0.0006</t>
-  </si>
-  <si>
-    <t>0.0031,0.2492,0.9830,0.0002</t>
-  </si>
-  <si>
-    <t>0.0047,0.4230,0.9652,0.0002</t>
-  </si>
-  <si>
-    <t>0.0352,0.1212,0.9135,0.0004</t>
-  </si>
-  <si>
-    <t>0.9078,0.0347,0.0242,0.0023</t>
-  </si>
-  <si>
-    <t>0.5889,0.2832,0.0202,0.0788</t>
-  </si>
-  <si>
-    <t>0.1082,0.0286,0.8823,0.0182</t>
-  </si>
-  <si>
-    <t>0.3859,0.5833,0.0929,0.0207</t>
-  </si>
-  <si>
-    <t>0.0258,0.0040,0.0016,0.9888</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.0006,0.9996</t>
-  </si>
-  <si>
-    <t>0.0009,0.1013,0.0002,0.9967</t>
-  </si>
-  <si>
-    <t>0.0071,0.0014,0.0026,0.9949</t>
-  </si>
-  <si>
-    <t>0.0047,0.9347,0.2274,0.0012</t>
-  </si>
-  <si>
-    <t>0.9830,0.0103,0.0022,0.0010</t>
-  </si>
-  <si>
-    <t>0.4419,0.6348,0.0057,0.0100</t>
-  </si>
-  <si>
-    <t>0.9841,0.0016,0.0011,0.0058</t>
-  </si>
-  <si>
-    <t>0.8946,0.1160,0.0146,0.0029</t>
-  </si>
-  <si>
-    <t>0.9681,0.0143,0.0040,0.0040</t>
-  </si>
-  <si>
-    <t>0.2704,0.0059,0.0099,0.8404</t>
-  </si>
-  <si>
-    <t>0.9468,0.0504,0.0097,0.0016</t>
-  </si>
-  <si>
-    <t>0.0036,0.0216,0.9737,0.0344</t>
-  </si>
-  <si>
-    <t>0.9284,0.0006,0.0045,0.0561</t>
-  </si>
-  <si>
-    <t>0.9676,0.0055,0.0060,0.0070</t>
-  </si>
-  <si>
-    <t>0.3140,0.6652,0.0645,0.0077</t>
-  </si>
-  <si>
-    <t>0.9499,0.0342,0.0018,0.0035</t>
-  </si>
-  <si>
-    <t>0.7982,0.2603,0.0190,0.0012</t>
-  </si>
-  <si>
-    <t>0.6715,0.3763,0.0283,0.0055</t>
-  </si>
-  <si>
-    <t>0.7850,0.1294,0.1138,0.0051</t>
-  </si>
-  <si>
-    <t>0.8617,0.1161,0.0212,0.0055</t>
-  </si>
-  <si>
-    <t>0.9758,0.0066,0.0027,0.0054</t>
-  </si>
-  <si>
-    <t>0.9948,0.0021,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9917,0.0022,0.0016,0.0009</t>
-  </si>
-  <si>
-    <t>0.9941,0.0003,0.0002,0.0027</t>
-  </si>
-  <si>
-    <t>0.9819,0.0032,0.0033,0.0039</t>
-  </si>
-  <si>
-    <t>0.9892,0.0028,0.0002,0.0029</t>
-  </si>
-  <si>
-    <t>0.9802,0.0031,0.0011,0.0082</t>
-  </si>
-  <si>
-    <t>0.9935,0.0003,0.0001,0.0035</t>
-  </si>
-  <si>
-    <t>0.6681,0.3911,0.0144,0.0125</t>
-  </si>
-  <si>
-    <t>0.6773,0.3483,0.0368,0.0009</t>
-  </si>
-  <si>
-    <t>0.8600,0.2465,0.0024,0.0007</t>
-  </si>
-  <si>
-    <t>0.4759,0.3185,0.3067,0.0158</t>
-  </si>
-  <si>
-    <t>0.9743,0.0358,0.0008,0.0008</t>
-  </si>
-  <si>
-    <t>0.9456,0.0143,0.0081,0.0186</t>
-  </si>
-  <si>
-    <t>0.9480,0.0479,0.0026,0.0049</t>
-  </si>
-  <si>
-    <t>0.8514,0.2905,0.0007,0.0009</t>
-  </si>
-  <si>
-    <t>0.0006,0.0084,0.9966,0.0015</t>
-  </si>
-  <si>
-    <t>0.9203,0.0612,0.0168,0.0062</t>
-  </si>
-  <si>
-    <t>0.0014,0.0141,0.9948,0.0003</t>
-  </si>
-  <si>
-    <t>0.0058,0.0124,0.9869,0.0021</t>
-  </si>
-  <si>
-    <t>0.3284,0.0047,0.8185,0.0006</t>
-  </si>
-  <si>
-    <t>0.0035,0.0260,0.9868,0.0010</t>
-  </si>
-  <si>
-    <t>0.0759,0.0244,0.9347,0.0003</t>
-  </si>
-  <si>
-    <t>0.0187,0.0011,0.9847,0.0007</t>
-  </si>
-  <si>
-    <t>0.0056,0.0034,0.9905,0.0023</t>
-  </si>
-  <si>
-    <t>0.1614,0.2447,0.6161,0.0039</t>
-  </si>
-  <si>
-    <t>0.4822,0.0165,0.6713,0.0008</t>
-  </si>
-  <si>
-    <t>0.0288,0.8694,0.2474,0.0044</t>
-  </si>
-  <si>
-    <t>0.3185,0.2338,0.5413,0.0077</t>
-  </si>
-  <si>
-    <t>0.4903,0.0966,0.4462,0.0020</t>
-  </si>
-  <si>
-    <t>0.6119,0.0253,0.5046,0.0009</t>
-  </si>
-  <si>
-    <t>0.7437,0.0343,0.2476,0.0193</t>
-  </si>
-  <si>
-    <t>0.3884,0.0323,0.7149,0.0015</t>
-  </si>
-  <si>
-    <t>0.8633,0.2377,0.0050,0.0007</t>
-  </si>
-  <si>
-    <t>0.1015,0.9221,0.0022,0.0010</t>
-  </si>
-  <si>
-    <t>0.9312,0.1127,0.0069,0.0006</t>
-  </si>
-  <si>
-    <t>0.9311,0.1410,0.0021,0.0003</t>
-  </si>
-  <si>
-    <t>0.2154,0.8577,0.0010,0.0018</t>
-  </si>
-  <si>
-    <t>0.6579,0.2219,0.0862,0.0440</t>
-  </si>
-  <si>
-    <t>0.7395,0.0039,0.2771,0.0144</t>
-  </si>
-  <si>
-    <t>0.8190,0.0368,0.0946,0.0211</t>
-  </si>
-  <si>
-    <t>0.4474,0.0030,0.7488,0.0018</t>
-  </si>
-  <si>
-    <t>0.7445,0.0375,0.1122,0.0929</t>
-  </si>
-  <si>
-    <t>0.0087,0.0147,0.9765,0.0104</t>
-  </si>
-  <si>
-    <t>0.0015,0.6902,0.9340,0.0021</t>
-  </si>
-  <si>
-    <t>0.0514,0.3063,0.8770,0.0067</t>
-  </si>
-  <si>
-    <t>0.1675,0.0312,0.8483,0.0127</t>
-  </si>
-  <si>
-    <t>0.0105,0.8051,0.5107,0.0049</t>
-  </si>
-  <si>
-    <t>0.9893,0.0017,0.0000,0.0035</t>
-  </si>
-  <si>
-    <t>0.9911,0.0024,0.0004,0.0021</t>
-  </si>
-  <si>
-    <t>0.9946,0.0025,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9874,0.0070,0.0014,0.0011</t>
-  </si>
-  <si>
-    <t>0.9674,0.0284,0.0013,0.0038</t>
-  </si>
-  <si>
-    <t>0.9767,0.0228,0.0022,0.0008</t>
-  </si>
-  <si>
-    <t>0.9796,0.0054,0.0008,0.0067</t>
-  </si>
-  <si>
-    <t>0.9659,0.0168,0.0068,0.0063</t>
-  </si>
-  <si>
-    <t>0.0040,0.0105,0.9855,0.0034</t>
-  </si>
-  <si>
-    <t>0.0288,0.7402,0.5531,0.0010</t>
-  </si>
-  <si>
-    <t>0.7313,0.1111,0.0252,0.1067</t>
-  </si>
-  <si>
-    <t>0.0111,0.0367,0.9831,0.0006</t>
-  </si>
-  <si>
-    <t>0.0008,0.0122,0.9898,0.0052</t>
-  </si>
-  <si>
-    <t>0.0050,0.0334,0.9831,0.0003</t>
-  </si>
-  <si>
-    <t>0.0059,0.0101,0.9922,0.0003</t>
-  </si>
-  <si>
-    <t>0.0391,0.0377,0.9098,0.0021</t>
-  </si>
-  <si>
-    <t>0.0142,0.0264,0.9788,0.0025</t>
-  </si>
-  <si>
-    <t>0.0220,0.0111,0.9671,0.0049</t>
-  </si>
-  <si>
-    <t>0.0627,0.2525,0.8615,0.0073</t>
-  </si>
-  <si>
-    <t>0.8160,0.0184,0.0910,0.0287</t>
-  </si>
-  <si>
-    <t>0.7592,0.0118,0.3224,0.0018</t>
-  </si>
-  <si>
-    <t>0.8907,0.0038,0.0657,0.0120</t>
-  </si>
-  <si>
-    <t>0.9774,0.0157,0.0004,0.0030</t>
-  </si>
-  <si>
-    <t>0.9791,0.0041,0.0004,0.0091</t>
-  </si>
-  <si>
-    <t>0.9950,0.0019,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9779,0.0258,0.0008,0.0007</t>
-  </si>
-  <si>
-    <t>0.9902,0.0011,0.0003,0.0041</t>
-  </si>
-  <si>
-    <t>0.9879,0.0171,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9932,0.0035,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9935,0.0033,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.0502,0.1221,0.8620,0.0039</t>
-  </si>
-  <si>
-    <t>0.0039,0.3354,0.9545,0.0023</t>
-  </si>
-  <si>
-    <t>0.0083,0.1622,0.9745,0.0004</t>
-  </si>
-  <si>
-    <t>0.0888,0.4398,0.4071,0.0006</t>
-  </si>
-  <si>
-    <t>0.0533,0.0129,0.9544,0.0026</t>
-  </si>
-  <si>
-    <t>0.1910,0.0350,0.7207,0.1242</t>
-  </si>
-  <si>
-    <t>0.1299,0.0106,0.9023,0.0020</t>
-  </si>
-  <si>
-    <t>0.2995,0.0488,0.6506,0.0615</t>
-  </si>
-  <si>
-    <t>0.8870,0.0181,0.0043,0.0599</t>
-  </si>
-  <si>
-    <t>0.0141,0.4066,0.0093,0.9551</t>
-  </si>
-  <si>
-    <t>0.0099,0.0135,0.0005,0.9935</t>
-  </si>
-  <si>
-    <t>0.0077,0.0002,0.0003,0.9976</t>
-  </si>
-  <si>
-    <t>0.0032,0.0005,0.0002,0.9987</t>
-  </si>
-  <si>
-    <t>0.8386,0.0423,0.0273,0.0573</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.8416,0.0175,0.0291,0.0748</t>
+  </si>
+  <si>
+    <t>0.0129,0.0017,0.0029,0.9928</t>
+  </si>
+  <si>
+    <t>0.8756,0.0138,0.0113,0.0649</t>
+  </si>
+  <si>
+    <t>0.0186,0.0040,0.0011,0.9924</t>
+  </si>
+  <si>
+    <t>0.9951,0.0028,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9939,0.0044,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9884,0.0106,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9891,0.0025,0.0017,0.0019</t>
+  </si>
+  <si>
+    <t>0.9942,0.0032,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9870,0.0093,0.0010,0.0012</t>
+  </si>
+  <si>
+    <t>0.9957,0.0020,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9953,0.0019,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.7918,0.1067,0.0934,0.0058</t>
+  </si>
+  <si>
+    <t>0.3847,0.0699,0.6549,0.0028</t>
+  </si>
+  <si>
+    <t>0.0714,0.0121,0.9532,0.0004</t>
+  </si>
+  <si>
+    <t>0.1631,0.0051,0.9054,0.0015</t>
+  </si>
+  <si>
+    <t>0.8260,0.0270,0.1707,0.0084</t>
+  </si>
+  <si>
+    <t>0.0069,0.9914,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0025,0.9953,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.5015,0.6257,0.0010,0.0024</t>
+  </si>
+  <si>
+    <t>0.0220,0.9746,0.0031,0.0009</t>
+  </si>
+  <si>
+    <t>0.0151,0.9804,0.0098,0.0005</t>
+  </si>
+  <si>
+    <t>0.3953,0.0016,0.5652,0.0213</t>
+  </si>
+  <si>
+    <t>0.5557,0.0439,0.4563,0.0148</t>
+  </si>
+  <si>
+    <t>0.0663,0.0087,0.9162,0.0191</t>
+  </si>
+  <si>
+    <t>0.2699,0.0207,0.7592,0.0295</t>
+  </si>
+  <si>
+    <t>0.0248,0.0031,0.9757,0.0019</t>
+  </si>
+  <si>
+    <t>0.2560,0.0025,0.8892,0.0007</t>
+  </si>
+  <si>
+    <t>0.0116,0.0041,0.9857,0.0027</t>
+  </si>
+  <si>
+    <t>0.3752,0.6803,0.0162,0.0031</t>
+  </si>
+  <si>
+    <t>0.5173,0.4246,0.1375,0.0071</t>
+  </si>
+  <si>
+    <t>0.0014,0.0047,0.9937,0.0055</t>
+  </si>
+  <si>
+    <t>0.0022,0.9718,0.1671,0.0001</t>
+  </si>
+  <si>
+    <t>0.8896,0.0600,0.0267,0.0143</t>
+  </si>
+  <si>
+    <t>0.6534,0.2536,0.1703,0.0148</t>
+  </si>
+  <si>
+    <t>0.8006,0.3414,0.0056,0.0011</t>
+  </si>
+  <si>
+    <t>0.1737,0.7821,0.2004,0.0097</t>
+  </si>
+  <si>
+    <t>0.0409,0.6031,0.6511,0.0158</t>
+  </si>
+  <si>
+    <t>0.0555,0.0247,0.8687,0.0871</t>
+  </si>
+  <si>
+    <t>0.1664,0.1827,0.7709,0.0489</t>
+  </si>
+  <si>
+    <t>0.6342,0.0012,0.2894,0.0190</t>
+  </si>
+  <si>
+    <t>0.0211,0.1402,0.9412,0.0036</t>
+  </si>
+  <si>
+    <t>0.0221,0.8932,0.0734,0.0003</t>
+  </si>
+  <si>
+    <t>0.0027,0.0539,0.9725,0.0143</t>
+  </si>
+  <si>
+    <t>0.4766,0.2713,0.1448,0.3357</t>
+  </si>
+  <si>
+    <t>0.0095,0.9717,0.0060,0.0099</t>
+  </si>
+  <si>
+    <t>0.0022,0.9830,0.0694,0.0006</t>
+  </si>
+  <si>
+    <t>0.0120,0.9684,0.0312,0.0080</t>
+  </si>
+  <si>
+    <t>0.0019,0.0568,0.9871,0.0036</t>
+  </si>
+  <si>
+    <t>0.0146,0.3616,0.9099,0.0018</t>
+  </si>
+  <si>
+    <t>0.1128,0.0341,0.8938,0.0065</t>
+  </si>
+  <si>
+    <t>0.0176,0.0016,0.9791,0.0052</t>
+  </si>
+  <si>
+    <t>0.0054,0.0078,0.9818,0.0106</t>
+  </si>
+  <si>
+    <t>0.0183,0.1011,0.9567,0.0090</t>
+  </si>
+  <si>
+    <t>0.9482,0.0851,0.0021,0.0008</t>
+  </si>
+  <si>
+    <t>0.9480,0.0052,0.0103,0.0185</t>
+  </si>
+  <si>
+    <t>0.9619,0.0451,0.0012,0.0014</t>
+  </si>
+  <si>
+    <t>0.0035,0.0267,0.9873,0.0036</t>
+  </si>
+  <si>
+    <t>0.9846,0.0053,0.0004,0.0038</t>
+  </si>
+  <si>
+    <t>0.9555,0.0531,0.0070,0.0016</t>
+  </si>
+  <si>
+    <t>0.9894,0.0077,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.9612,0.8169,0.0003</t>
+  </si>
+  <si>
+    <t>0.0022,0.0046,0.9913,0.0043</t>
+  </si>
+  <si>
+    <t>0.0058,0.0096,0.9846,0.0049</t>
+  </si>
+  <si>
+    <t>0.0052,0.7341,0.9424,0.0012</t>
+  </si>
+  <si>
+    <t>0.0138,0.0039,0.9810,0.0061</t>
+  </si>
+  <si>
+    <t>0.0566,0.7638,0.3184,0.0019</t>
+  </si>
+  <si>
+    <t>0.0074,0.9883,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.6135,0.0746,0.4556,0.0248</t>
+  </si>
+  <si>
+    <t>0.4596,0.4846,0.1850,0.0123</t>
+  </si>
+  <si>
+    <t>0.0033,0.0112,0.9893,0.0012</t>
+  </si>
+  <si>
+    <t>0.0023,0.7450,0.9485,0.0005</t>
+  </si>
+  <si>
+    <t>0.0017,0.6019,0.9797,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9805,0.5027,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.9772,0.8892,0.0000</t>
+  </si>
+  <si>
+    <t>0.1227,0.0052,0.0745,0.8054</t>
+  </si>
+  <si>
+    <t>0.0022,0.3436,0.0013,0.9824</t>
+  </si>
+  <si>
+    <t>0.0023,0.0035,0.0002,0.9985</t>
+  </si>
+  <si>
+    <t>0.0137,0.0141,0.0020,0.9904</t>
+  </si>
+  <si>
+    <t>0.0507,0.0021,0.0203,0.9629</t>
+  </si>
+  <si>
+    <t>0.0029,0.0038,0.0003,0.9979</t>
+  </si>
+  <si>
+    <t>0.0005,0.9802,0.7942,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.6950,0.9876,0.0002</t>
+  </si>
+  <si>
+    <t>0.0216,0.2763,0.9171,0.0005</t>
+  </si>
+  <si>
+    <t>0.0036,0.8217,0.8985,0.0010</t>
+  </si>
+  <si>
+    <t>0.0005,0.9423,0.9166,0.0000</t>
+  </si>
+  <si>
+    <t>0.0121,0.7627,0.7647,0.0019</t>
+  </si>
+  <si>
+    <t>0.9810,0.0243,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9253,0.1081,0.0068,0.0017</t>
+  </si>
+  <si>
+    <t>0.9866,0.0131,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9944,0.0029,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9884,0.0059,0.0003,0.0017</t>
+  </si>
+  <si>
+    <t>0.9855,0.0116,0.0018,0.0007</t>
+  </si>
+  <si>
+    <t>0.9634,0.0325,0.0003,0.0024</t>
+  </si>
+  <si>
+    <t>0.9927,0.0074,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9776,0.0318,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.9973,0.0014,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9927,0.0037,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9946,0.0039,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9962,0.0009,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9968,0.0010,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9925,0.0025,0.0005,0.0013</t>
+  </si>
+  <si>
+    <t>0.0385,0.0058,0.9675,0.0054</t>
+  </si>
+  <si>
+    <t>0.3769,0.0191,0.7265,0.0029</t>
+  </si>
+  <si>
+    <t>0.9044,0.0020,0.1505,0.0011</t>
+  </si>
+  <si>
+    <t>0.3782,0.0068,0.7401,0.0062</t>
+  </si>
+  <si>
+    <t>0.0540,0.9523,0.0048,0.0011</t>
+  </si>
+  <si>
+    <t>0.0228,0.9632,0.0233,0.0013</t>
+  </si>
+  <si>
+    <t>0.0845,0.9098,0.0007,0.0035</t>
+  </si>
+  <si>
+    <t>0.0176,0.9788,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.2213,0.8422,0.0251,0.0035</t>
+  </si>
+  <si>
+    <t>0.0022,0.9947,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.6954,0.4049,0.0143,0.0019</t>
+  </si>
+  <si>
+    <t>0.8080,0.0187,0.1530,0.0125</t>
+  </si>
+  <si>
+    <t>0.3839,0.0302,0.6981,0.0039</t>
+  </si>
+  <si>
+    <t>0.1961,0.4430,0.0475,0.3187</t>
+  </si>
+  <si>
+    <t>0.5613,0.1094,0.3804,0.0233</t>
+  </si>
+  <si>
+    <t>0.0699,0.3062,0.0106,0.8775</t>
+  </si>
+  <si>
+    <t>0.0089,0.9859,0.0056,0.0003</t>
+  </si>
+  <si>
+    <t>0.0056,0.9833,0.0071,0.0013</t>
+  </si>
+  <si>
+    <t>0.0021,0.9572,0.0027,0.2189</t>
+  </si>
+  <si>
+    <t>0.0015,0.8318,0.9597,0.0006</t>
+  </si>
+  <si>
+    <t>0.0139,0.9776,0.0401,0.0005</t>
+  </si>
+  <si>
+    <t>0.4930,0.4371,0.0850,0.0011</t>
+  </si>
+  <si>
+    <t>0.4288,0.6142,0.0250,0.0006</t>
+  </si>
+  <si>
+    <t>0.9393,0.0488,0.0066,0.0063</t>
+  </si>
+  <si>
+    <t>0.9945,0.0008,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9914,0.0026,0.0011,0.0014</t>
+  </si>
+  <si>
+    <t>0.9887,0.0030,0.0026,0.0011</t>
+  </si>
+  <si>
+    <t>0.9930,0.0017,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9336,0.0278,0.0268,0.0056</t>
+  </si>
+  <si>
+    <t>0.9871,0.0010,0.0003,0.0065</t>
+  </si>
+  <si>
+    <t>0.9854,0.0032,0.0034,0.0025</t>
+  </si>
+  <si>
+    <t>0.0059,0.7614,0.9234,0.0010</t>
+  </si>
+  <si>
+    <t>0.0023,0.8963,0.7202,0.0001</t>
+  </si>
+  <si>
+    <t>0.0054,0.5665,0.8914,0.0005</t>
+  </si>
+  <si>
+    <t>0.0217,0.2713,0.8702,0.0009</t>
+  </si>
+  <si>
+    <t>0.7066,0.2230,0.0257,0.0219</t>
+  </si>
+  <si>
+    <t>0.7405,0.0323,0.2795,0.0114</t>
+  </si>
+  <si>
+    <t>0.2052,0.0097,0.8489,0.0096</t>
+  </si>
+  <si>
+    <t>0.3742,0.3584,0.2897,0.0062</t>
+  </si>
+  <si>
+    <t>0.2328,0.0021,0.0024,0.8944</t>
+  </si>
+  <si>
+    <t>0.0006,0.0037,0.0008,0.9990</t>
+  </si>
+  <si>
+    <t>0.0035,0.0090,0.0009,0.9968</t>
+  </si>
+  <si>
+    <t>0.0310,0.0054,0.0435,0.9622</t>
+  </si>
+  <si>
+    <t>0.0042,0.9157,0.5324,0.0007</t>
+  </si>
+  <si>
+    <t>0.9841,0.0084,0.0028,0.0012</t>
+  </si>
+  <si>
+    <t>0.5555,0.5380,0.0116,0.0135</t>
+  </si>
+  <si>
+    <t>0.9781,0.0034,0.0024,0.0074</t>
+  </si>
+  <si>
+    <t>0.5377,0.6069,0.0076,0.0018</t>
+  </si>
+  <si>
+    <t>0.9845,0.0032,0.0015,0.0036</t>
+  </si>
+  <si>
+    <t>0.8508,0.0014,0.0071,0.1524</t>
+  </si>
+  <si>
+    <t>0.9840,0.0026,0.0027,0.0035</t>
+  </si>
+  <si>
+    <t>0.0054,0.0345,0.9268,0.1504</t>
+  </si>
+  <si>
+    <t>0.9218,0.0036,0.0201,0.0276</t>
+  </si>
+  <si>
+    <t>0.9797,0.0030,0.0032,0.0047</t>
+  </si>
+  <si>
+    <t>0.5143,0.5646,0.0236,0.0045</t>
+  </si>
+  <si>
+    <t>0.6101,0.4874,0.0076,0.0042</t>
+  </si>
+  <si>
+    <t>0.8818,0.0640,0.0509,0.0021</t>
+  </si>
+  <si>
+    <t>0.5966,0.4102,0.0702,0.0248</t>
+  </si>
+  <si>
+    <t>0.8434,0.1711,0.0158,0.0031</t>
+  </si>
+  <si>
+    <t>0.7754,0.2709,0.0141,0.0058</t>
+  </si>
+  <si>
+    <t>0.9895,0.0068,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9906,0.0021,0.0004,0.0021</t>
+  </si>
+  <si>
+    <t>0.9749,0.0137,0.0029,0.0029</t>
+  </si>
+  <si>
+    <t>0.9960,0.0002,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.9888,0.0061,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9753,0.0106,0.0021,0.0048</t>
+  </si>
+  <si>
+    <t>0.9910,0.0006,0.0004,0.0041</t>
+  </si>
+  <si>
+    <t>0.9876,0.0045,0.0024,0.0012</t>
+  </si>
+  <si>
+    <t>0.5145,0.6266,0.0064,0.0035</t>
+  </si>
+  <si>
+    <t>0.0837,0.9265,0.0071,0.0017</t>
+  </si>
+  <si>
+    <t>0.5189,0.5827,0.0241,0.0018</t>
+  </si>
+  <si>
+    <t>0.7896,0.1685,0.1086,0.0105</t>
+  </si>
+  <si>
+    <t>0.9409,0.1017,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.9519,0.0311,0.0048,0.0081</t>
+  </si>
+  <si>
+    <t>0.9662,0.0512,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.1728,0.8524,0.0076,0.0033</t>
+  </si>
+  <si>
+    <t>0.0014,0.0044,0.9968,0.0010</t>
+  </si>
+  <si>
+    <t>0.8807,0.0773,0.0457,0.0038</t>
+  </si>
+  <si>
+    <t>0.0195,0.0022,0.9873,0.0004</t>
+  </si>
+  <si>
+    <t>0.0069,0.0399,0.9832,0.0008</t>
+  </si>
+  <si>
+    <t>0.0485,0.0153,0.9547,0.0012</t>
+  </si>
+  <si>
+    <t>0.1090,0.0234,0.9234,0.0014</t>
+  </si>
+  <si>
+    <t>0.0107,0.0102,0.9845,0.0006</t>
+  </si>
+  <si>
+    <t>0.0065,0.0067,0.9917,0.0002</t>
+  </si>
+  <si>
+    <t>0.0818,0.0103,0.9405,0.0001</t>
+  </si>
+  <si>
+    <t>0.3929,0.2147,0.4453,0.0156</t>
+  </si>
+  <si>
+    <t>0.1148,0.0190,0.9323,0.0020</t>
+  </si>
+  <si>
+    <t>0.5373,0.1966,0.3088,0.0133</t>
+  </si>
+  <si>
+    <t>0.1962,0.3080,0.4805,0.0019</t>
+  </si>
+  <si>
+    <t>0.0936,0.5665,0.2376,0.0006</t>
+  </si>
+  <si>
+    <t>0.6410,0.1620,0.1549,0.0013</t>
+  </si>
+  <si>
+    <t>0.7115,0.1353,0.1345,0.0078</t>
+  </si>
+  <si>
+    <t>0.2884,0.0509,0.7600,0.0017</t>
+  </si>
+  <si>
+    <t>0.2956,0.7361,0.0287,0.0004</t>
+  </si>
+  <si>
+    <t>0.2031,0.8803,0.0022,0.0010</t>
+  </si>
+  <si>
+    <t>0.9305,0.0844,0.0074,0.0016</t>
+  </si>
+  <si>
+    <t>0.9807,0.0235,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.5187,0.6516,0.0029,0.0012</t>
+  </si>
+  <si>
+    <t>0.6287,0.2521,0.1128,0.0175</t>
+  </si>
+  <si>
+    <t>0.8799,0.0119,0.0891,0.0075</t>
+  </si>
+  <si>
+    <t>0.8051,0.0287,0.1279,0.0197</t>
+  </si>
+  <si>
+    <t>0.7384,0.0113,0.2947,0.0117</t>
+  </si>
+  <si>
+    <t>0.7179,0.0096,0.2073,0.0393</t>
+  </si>
+  <si>
+    <t>0.0077,0.0067,0.9423,0.1627</t>
+  </si>
+  <si>
+    <t>0.0728,0.0995,0.8988,0.0043</t>
+  </si>
+  <si>
+    <t>0.0333,0.0731,0.9381,0.0058</t>
+  </si>
+  <si>
+    <t>0.0349,0.1585,0.8648,0.0168</t>
+  </si>
+  <si>
+    <t>0.0133,0.6026,0.6497,0.0013</t>
+  </si>
+  <si>
+    <t>0.9867,0.0089,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9741,0.0363,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.9849,0.0074,0.0003,0.0025</t>
+  </si>
+  <si>
+    <t>0.9896,0.0049,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9534,0.0521,0.0065,0.0014</t>
+  </si>
+  <si>
+    <t>0.9920,0.0016,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.9911,0.0018,0.0002,0.0023</t>
+  </si>
+  <si>
+    <t>0.9931,0.0014,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.0691,0.1083,0.8972,0.0043</t>
+  </si>
+  <si>
+    <t>0.5580,0.2483,0.2484,0.0301</t>
+  </si>
+  <si>
+    <t>0.9041,0.0193,0.0500,0.0089</t>
+  </si>
+  <si>
+    <t>0.0194,0.0030,0.9874,0.0007</t>
+  </si>
+  <si>
+    <t>0.0051,0.0076,0.9869,0.0024</t>
+  </si>
+  <si>
+    <t>0.0116,0.1118,0.9319,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0070,0.9952,0.0009</t>
+  </si>
+  <si>
+    <t>0.0668,0.0437,0.9095,0.0049</t>
+  </si>
+  <si>
+    <t>0.0007,0.0047,0.9973,0.0005</t>
+  </si>
+  <si>
+    <t>0.0284,0.2965,0.7883,0.0125</t>
+  </si>
+  <si>
+    <t>0.0078,0.0254,0.9848,0.0030</t>
+  </si>
+  <si>
+    <t>0.4508,0.0758,0.5235,0.0437</t>
+  </si>
+  <si>
+    <t>0.7774,0.0187,0.2104,0.0134</t>
+  </si>
+  <si>
+    <t>0.8777,0.0134,0.0864,0.0057</t>
+  </si>
+  <si>
+    <t>0.9849,0.0084,0.0016,0.0013</t>
+  </si>
+  <si>
+    <t>0.9859,0.0152,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9853,0.0137,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.9730,0.0279,0.0037,0.0008</t>
+  </si>
+  <si>
+    <t>0.9927,0.0032,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9919,0.0064,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.9967,0.0010,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9758,0.0180,0.0014,0.0031</t>
+  </si>
+  <si>
+    <t>0.0403,0.0496,0.9349,0.0032</t>
+  </si>
+  <si>
+    <t>0.0034,0.0263,0.9893,0.0007</t>
+  </si>
+  <si>
+    <t>0.0042,0.4133,0.9577,0.0006</t>
+  </si>
+  <si>
+    <t>0.1361,0.0105,0.9089,0.0028</t>
+  </si>
+  <si>
+    <t>0.0072,0.0097,0.9859,0.0033</t>
+  </si>
+  <si>
+    <t>0.0475,0.0089,0.9489,0.0123</t>
+  </si>
+  <si>
+    <t>0.2064,0.0131,0.7856,0.0418</t>
+  </si>
+  <si>
+    <t>0.1285,0.1862,0.6332,0.1691</t>
+  </si>
+  <si>
+    <t>0.1321,0.0045,0.0061,0.9386</t>
+  </si>
+  <si>
+    <t>0.0768,0.4533,0.0358,0.8621</t>
+  </si>
+  <si>
+    <t>0.0134,0.0039,0.0018,0.9931</t>
+  </si>
+  <si>
+    <t>0.0011,0.0004,0.0030,0.9982</t>
+  </si>
+  <si>
+    <t>0.0046,0.0008,0.0040,0.9955</t>
+  </si>
+  <si>
+    <t>0.8097,0.0326,0.0571,0.0566</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2130,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2225,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2267,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2284,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2368,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2382,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2438,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2449,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2477,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2519,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2911,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2925,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2981,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3121,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3135,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3166,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3544,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3558,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3569,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3600,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3614,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3670,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3695,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3712,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3835,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3849,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3863,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4003,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4031,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4059,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4087,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4157,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4202,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4353,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4367,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4381,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4398,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,10 +4451,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4591,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4647,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4661,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4678,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4692,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4703,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4720,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4734,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4759,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4776,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4857,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4902,7 @@
         <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5039,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5179,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5375,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5445,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5518,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
